--- a/daily_data/mcgm_2026-07-01.xlsx
+++ b/daily_data/mcgm_2026-07-01.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:47</t>
+          <t>2026-07-01 06:03:42</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -496,7 +496,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:15:00.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -506,34 +506,34 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1003.2</t>
+          <t>1003.1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:48</t>
+          <t>2026-07-01 06:03:43</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -585,7 +585,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:49</t>
+          <t>2026-07-01 06:03:44</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -600,7 +600,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1004.1</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:50</t>
+          <t>2026-07-01 06:03:45</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -652,7 +652,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -667,29 +667,29 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1004.1</t>
+          <t>1003.8</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>9.7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:51</t>
+          <t>2026-07-01 06:03:47</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -704,7 +704,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -719,17 +719,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1005.2</t>
+          <t>1005.1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:52</t>
+          <t>2026-07-01 06:03:48</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -756,44 +756,44 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:00:00.0</t>
+          <t>2026-07-01 11:15:00.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>999.9</t>
+          <t>1002.1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:53</t>
+          <t>2026-07-01 06:03:49</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -808,22 +808,22 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -838,14 +838,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:55</t>
+          <t>2026-07-01 06:03:50</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -860,22 +860,22 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -890,14 +890,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:57</t>
+          <t>2026-07-01 06:03:51</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -912,22 +912,22 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:58</t>
+          <t>2026-07-01 06:03:52</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -964,22 +964,22 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01 05:43:59</t>
+          <t>2026-07-01 06:03:53</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1016,7 +1016,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1031,29 +1031,29 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:00</t>
+          <t>2026-07-01 06:03:54</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1105,7 +1105,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:01</t>
+          <t>2026-07-01 06:03:55</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1120,7 +1120,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1005.2</t>
+          <t>1005.1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:02</t>
+          <t>2026-07-01 06:03:56</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1172,7 +1172,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1187,29 +1187,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1003.0</t>
+          <t>1002.7</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:03</t>
+          <t>2026-07-01 06:03:57</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1224,7 +1224,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1239,29 +1239,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1003.8</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:04</t>
+          <t>2026-07-01 06:03:58</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1276,27 +1276,27 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:05</t>
+          <t>2026-07-01 06:03:59</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1328,12 +1328,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1358,14 +1358,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:06</t>
+          <t>2026-07-01 06:04:00</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1380,32 +1380,32 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>112.4</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1003.5</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:07</t>
+          <t>2026-07-01 06:04:01</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1432,32 +1432,32 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>112.4</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1003.5</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:08</t>
+          <t>2026-07-01 06:04:03</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1484,44 +1484,44 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>105.4</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:09</t>
+          <t>2026-07-01 06:04:04</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1536,7 +1536,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1546,34 +1546,34 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.5</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>11.3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:10</t>
+          <t>2026-07-01 06:04:05</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1588,22 +1588,22 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>127.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1613,19 +1613,19 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:11</t>
+          <t>2026-07-01 06:04:06</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1640,32 +1640,32 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>116.8</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1004.1</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:13</t>
+          <t>2026-07-01 06:04:07</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1692,22 +1692,22 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1717,19 +1717,19 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1003.5</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:14</t>
+          <t>2026-07-01 06:04:08</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1744,27 +1744,27 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:15</t>
+          <t>2026-07-01 06:04:09</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1796,27 +1796,27 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:16</t>
+          <t>2026-07-01 06:04:10</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1848,22 +1848,22 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1873,19 +1873,19 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1003.5</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:17</t>
+          <t>2026-07-01 06:04:11</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1937,7 +1937,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:18</t>
+          <t>2026-07-01 06:04:12</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1952,27 +1952,27 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>19.80</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>118.8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1982,14 +1982,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:19</t>
+          <t>2026-07-01 06:04:13</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2004,7 +2004,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2019,29 +2019,29 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:20</t>
+          <t>2026-07-01 06:04:15</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2056,7 +2056,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>116.4</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>1004.2</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:21</t>
+          <t>2026-07-01 06:04:16</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2145,7 +2145,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:22</t>
+          <t>2026-07-01 06:04:17</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2160,22 +2160,22 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>127.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2185,19 +2185,19 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:23</t>
+          <t>2026-07-01 06:04:18</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2212,22 +2212,22 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>134.4</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2237,19 +2237,19 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1004.9</t>
+          <t>1004.8</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:24</t>
+          <t>2026-07-01 06:04:19</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2301,7 +2301,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:25</t>
+          <t>2026-07-01 06:04:20</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2316,7 +2316,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2336,24 +2336,24 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>1004.2</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:26</t>
+          <t>2026-07-01 06:04:21</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2368,7 +2368,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2388,24 +2388,24 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>1004.2</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:27</t>
+          <t>2026-07-01 06:04:22</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2420,7 +2420,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2445,19 +2445,19 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1004.2</t>
+          <t>1003.8</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:28</t>
+          <t>2026-07-01 06:04:23</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2472,7 +2472,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2509,7 +2509,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:29</t>
+          <t>2026-07-01 06:04:25</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2524,44 +2524,44 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>126.6</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1001.8</t>
+          <t>1002.0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:30</t>
+          <t>2026-07-01 06:04:26</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2576,44 +2576,44 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>126.6</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1001.8</t>
+          <t>1002.0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:32</t>
+          <t>2026-07-01 06:04:27</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2628,44 +2628,44 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>143.6</t>
+          <t>156.2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1003.1</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:33</t>
+          <t>2026-07-01 06:04:28</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2717,7 +2717,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:34</t>
+          <t>2026-07-01 06:04:29</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2769,7 +2769,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:35</t>
+          <t>2026-07-01 06:04:30</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2784,22 +2784,22 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>109.2</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1003.8</t>
+          <t>1003.6</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:36</t>
+          <t>2026-07-01 06:04:31</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2836,22 +2836,22 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>109.2</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2861,19 +2861,19 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1003.8</t>
+          <t>1003.6</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:38</t>
+          <t>2026-07-01 06:04:32</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2888,7 +2888,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1002.2</t>
+          <t>1002.0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2925,7 +2925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:39</t>
+          <t>2026-07-01 06:04:33</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2940,7 +2940,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1000.9</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2977,7 +2977,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:40</t>
+          <t>2026-07-01 06:04:34</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2992,7 +2992,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3017,19 +3017,19 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.9</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:41</t>
+          <t>2026-07-01 06:04:35</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3044,7 +3044,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3054,17 +3054,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>113.6</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:42</t>
+          <t>2026-07-01 06:04:36</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3096,22 +3096,22 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138.6</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3133,7 +3133,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:43</t>
+          <t>2026-07-01 06:04:37</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3148,7 +3148,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3158,22 +3158,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>127.6</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1003.2</t>
+          <t>1002.8</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3185,7 +3185,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:44</t>
+          <t>2026-07-01 06:04:38</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3200,7 +3200,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3215,29 +3215,29 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1003.8</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:45</t>
+          <t>2026-07-01 06:04:39</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3252,32 +3252,32 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>116.8</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1004.1</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3289,7 +3289,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:46</t>
+          <t>2026-07-01 06:04:40</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3304,22 +3304,22 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>100.8</t>
+          <t>120.8</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1003.5</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3341,7 +3341,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:47</t>
+          <t>2026-07-01 06:04:42</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3356,7 +3356,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3371,29 +3371,29 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1004.2</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:48</t>
+          <t>2026-07-01 06:04:43</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3408,7 +3408,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:15:00.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3423,17 +3423,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1002.9</t>
+          <t>1002.8</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:49</t>
+          <t>2026-07-01 06:04:44</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3460,22 +3460,22 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3490,14 +3490,14 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:50</t>
+          <t>2026-07-01 06:04:45</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3512,44 +3512,44 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1002.1</t>
+          <t>1002.0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:51</t>
+          <t>2026-07-01 06:04:46</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3564,22 +3564,22 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3589,19 +3589,19 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.5</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:52</t>
+          <t>2026-07-01 06:04:47</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3616,44 +3616,44 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1002.1</t>
+          <t>1002.0</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:53</t>
+          <t>2026-07-01 06:04:48</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3668,44 +3668,44 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-01 00:00:00.0</t>
+          <t>2026-07-01 11:15:00.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>999.9</t>
+          <t>1002.1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:54</t>
+          <t>2026-07-01 06:04:49</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3720,27 +3720,27 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3750,14 +3750,14 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:55</t>
+          <t>2026-07-01 06:04:50</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3772,7 +3772,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3797,19 +3797,19 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.2</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>12.9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:56</t>
+          <t>2026-07-01 06:04:51</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3824,7 +3824,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3849,19 +3849,19 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1004.4</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>19.3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:57</t>
+          <t>2026-07-01 06:04:52</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3876,7 +3876,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>1004.3</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -3913,7 +3913,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:58</t>
+          <t>2026-07-01 06:04:53</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3928,12 +3928,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3958,14 +3958,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-01 05:44:59</t>
+          <t>2026-07-01 06:04:54</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4017,7 +4017,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:00</t>
+          <t>2026-07-01 06:04:55</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4032,7 +4032,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4057,19 +4057,19 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:02</t>
+          <t>2026-07-01 06:04:56</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4084,7 +4084,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4109,19 +4109,19 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:03</t>
+          <t>2026-07-01 06:04:57</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4136,7 +4136,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1000.9</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4173,7 +4173,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:04</t>
+          <t>2026-07-01 06:04:58</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -4188,22 +4188,22 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4213,19 +4213,19 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1003.9</t>
+          <t>1003.8</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:05</t>
+          <t>2026-07-01 06:05:00</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -4240,22 +4240,22 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>138.6</t>
+          <t>141.6</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4265,19 +4265,19 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1001.8</t>
+          <t>1001.7</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:06</t>
+          <t>2026-07-01 06:05:01</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4292,22 +4292,22 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>141.6</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4317,19 +4317,19 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>998.9</t>
+          <t>999.0</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:07</t>
+          <t>2026-07-01 06:05:02</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4344,7 +4344,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>116.4</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>1004.2</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:08</t>
+          <t>2026-07-01 06:05:03</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4396,7 +4396,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4421,19 +4421,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.3</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:09</t>
+          <t>2026-07-01 06:05:04</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -4448,22 +4448,22 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>182.2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4485,7 +4485,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:10</t>
+          <t>2026-07-01 06:05:05</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4537,7 +4537,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:11</t>
+          <t>2026-07-01 06:05:06</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4589,7 +4589,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:12</t>
+          <t>2026-07-01 06:05:07</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4641,7 +4641,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:13</t>
+          <t>2026-07-01 06:05:08</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -4656,22 +4656,22 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>100.8</t>
+          <t>120.8</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1003.5</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -4693,7 +4693,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:14</t>
+          <t>2026-07-01 06:05:10</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4708,7 +4708,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4733,19 +4733,19 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1004.3</t>
+          <t>1004.1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:15</t>
+          <t>2026-07-01 06:05:11</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -4760,7 +4760,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4775,17 +4775,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4797,7 +4797,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:16</t>
+          <t>2026-07-01 06:05:12</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4812,44 +4812,44 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>160.8</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1004.9</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:17</t>
+          <t>2026-07-01 06:05:13</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -4864,22 +4864,22 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>121.2</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4889,19 +4889,19 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>1003.2</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:18</t>
+          <t>2026-07-01 06:05:14</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4916,44 +4916,44 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>148.4</t>
+          <t>151.2</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1005.0</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:19</t>
+          <t>2026-07-01 06:05:15</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -4968,44 +4968,44 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1002.9</t>
+          <t>1003.2</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>9.7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:20</t>
+          <t>2026-07-01 06:05:16</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -5020,22 +5020,22 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>121.2</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5045,19 +5045,19 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>1003.2</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:21</t>
+          <t>2026-07-01 06:05:17</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -5109,7 +5109,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:22</t>
+          <t>2026-07-01 06:05:18</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -5124,7 +5124,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5154,14 +5154,14 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:23</t>
+          <t>2026-07-01 06:05:20</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -5176,7 +5176,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1004.1</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5213,7 +5213,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:24</t>
+          <t>2026-07-01 06:05:21</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -5228,22 +5228,22 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>138.6</t>
+          <t>141.6</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5253,19 +5253,19 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1001.8</t>
+          <t>1001.7</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:26</t>
+          <t>2026-07-01 06:05:22</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -5280,22 +5280,22 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>141.6</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5305,19 +5305,19 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>998.9</t>
+          <t>999.0</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:27</t>
+          <t>2026-07-01 06:05:23</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -5332,12 +5332,12 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:15:00.0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5352,24 +5352,24 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>1002.9</t>
+          <t>1002.8</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:28</t>
+          <t>2026-07-01 06:05:24</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -5384,22 +5384,22 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>116.4</t>
+          <t>118.4</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5421,7 +5421,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:29</t>
+          <t>2026-07-01 06:05:25</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -5436,22 +5436,22 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>116.4</t>
+          <t>118.4</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5473,7 +5473,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:30</t>
+          <t>2026-07-01 06:05:26</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -5488,12 +5488,12 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5518,14 +5518,14 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:31</t>
+          <t>2026-07-01 06:05:27</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -5540,7 +5540,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5570,14 +5570,14 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:32</t>
+          <t>2026-07-01 06:05:28</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -5592,7 +5592,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5602,34 +5602,34 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.4</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.5</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:33</t>
+          <t>2026-07-01 06:05:29</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -5644,7 +5644,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1005.0</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5681,7 +5681,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:34</t>
+          <t>2026-07-01 06:05:30</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -5733,7 +5733,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:35</t>
+          <t>2026-07-01 06:05:31</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -5748,44 +5748,44 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>105.4</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:36</t>
+          <t>2026-07-01 06:05:32</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -5800,7 +5800,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5825,19 +5825,19 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.6</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:37</t>
+          <t>2026-07-01 06:05:33</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -5889,7 +5889,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:38</t>
+          <t>2026-07-01 06:05:34</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -5904,7 +5904,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5919,29 +5919,29 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1004.2</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:39</t>
+          <t>2026-07-01 06:05:35</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -5993,7 +5993,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:40</t>
+          <t>2026-07-01 06:05:36</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -6008,7 +6008,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6033,19 +6033,19 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.6</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:41</t>
+          <t>2026-07-01 06:05:38</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -6060,7 +6060,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>1004.1</t>
+          <t>1003.8</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>9.7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:42</t>
+          <t>2026-07-01 06:05:39</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -6112,22 +6112,22 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>130.6</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>1004.4</t>
+          <t>1004.3</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6149,7 +6149,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:43</t>
+          <t>2026-07-01 06:05:40</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -6164,22 +6164,22 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>157.8</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6194,14 +6194,14 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:44</t>
+          <t>2026-07-01 06:05:41</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -6216,22 +6216,22 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>130.6</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1004.4</t>
+          <t>1004.3</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6253,7 +6253,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:45</t>
+          <t>2026-07-01 06:05:42</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -6305,7 +6305,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:46</t>
+          <t>2026-07-01 06:05:43</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -6320,7 +6320,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>1004.3</t>
+          <t>1004.2</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:47</t>
+          <t>2026-07-01 06:05:44</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -6372,44 +6372,44 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>1003.4</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:48</t>
+          <t>2026-07-01 06:05:45</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -6424,7 +6424,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6449,19 +6449,19 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.6</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:50</t>
+          <t>2026-07-01 06:05:46</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -6476,22 +6476,22 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>948.7</t>
+          <t>948.8</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6513,7 +6513,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:52</t>
+          <t>2026-07-01 06:05:47</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -6528,7 +6528,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6553,19 +6553,19 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>1004.4</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>19.3</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:53</t>
+          <t>2026-07-01 06:05:48</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -6617,7 +6617,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:54</t>
+          <t>2026-07-01 06:05:49</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -6632,22 +6632,22 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6657,19 +6657,19 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.5</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:55</t>
+          <t>2026-07-01 06:05:50</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -6684,22 +6684,22 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6714,14 +6714,14 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:56</t>
+          <t>2026-07-01 06:05:51</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -6773,7 +6773,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:57</t>
+          <t>2026-07-01 06:05:52</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -6788,22 +6788,22 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6813,19 +6813,19 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>1005.6</t>
+          <t>1005.9</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:58</t>
+          <t>2026-07-01 06:05:53</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -6840,7 +6840,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6850,22 +6850,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>127.6</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>1003.2</t>
+          <t>1002.8</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -6877,7 +6877,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-01 05:45:59</t>
+          <t>2026-07-01 06:05:55</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -6929,7 +6929,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:00</t>
+          <t>2026-07-01 06:05:56</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -6981,7 +6981,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:01</t>
+          <t>2026-07-01 06:05:57</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -6996,22 +6996,22 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>1005.0</t>
+          <t>1004.9</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7033,7 +7033,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:02</t>
+          <t>2026-07-01 06:05:58</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -7048,22 +7048,22 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>108.8</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7073,19 +7073,19 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>1002.5</t>
+          <t>1002.4</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:03</t>
+          <t>2026-07-01 06:05:59</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -7100,22 +7100,22 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>948.7</t>
+          <t>948.8</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -7137,7 +7137,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:04</t>
+          <t>2026-07-01 06:06:00</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -7152,22 +7152,22 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1004.4</t>
+          <t>1004.6</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -7189,7 +7189,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:05</t>
+          <t>2026-07-01 06:06:01</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -7204,22 +7204,22 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1004.4</t>
+          <t>1004.6</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -7241,7 +7241,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:06</t>
+          <t>2026-07-01 06:06:02</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -7256,7 +7256,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7271,17 +7271,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -7293,7 +7293,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:07</t>
+          <t>2026-07-01 06:06:03</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -7308,27 +7308,27 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>181.6</t>
+          <t>181.8</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -7345,7 +7345,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:08</t>
+          <t>2026-07-01 06:06:04</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -7360,7 +7360,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>1005.0</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -7397,7 +7397,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:09</t>
+          <t>2026-07-01 06:06:05</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -7412,22 +7412,22 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7442,14 +7442,14 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:10</t>
+          <t>2026-07-01 06:06:06</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -7464,7 +7464,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7489,19 +7489,19 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>1002.2</t>
+          <t>1002.1</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:11</t>
+          <t>2026-07-01 06:06:07</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -7553,7 +7553,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:12</t>
+          <t>2026-07-01 06:06:08</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -7568,7 +7568,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -7578,34 +7578,34 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>1004.0</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:13</t>
+          <t>2026-07-01 06:06:09</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -7620,12 +7620,12 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:15:00.0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -7640,24 +7640,24 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>1002.9</t>
+          <t>1002.8</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:14</t>
+          <t>2026-07-01 06:06:10</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -7672,22 +7672,22 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>114.2</t>
+          <t>134.6</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7702,14 +7702,14 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>14.5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:16</t>
+          <t>2026-07-01 06:06:12</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -7724,7 +7724,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -7734,22 +7734,22 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>139.6</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -7761,7 +7761,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:17</t>
+          <t>2026-07-01 06:06:13</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -7776,17 +7776,17 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>178.6</t>
+          <t>184.4</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7801,19 +7801,19 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>1002.6</t>
+          <t>1002.2</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:18</t>
+          <t>2026-07-01 06:06:14</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -7828,22 +7828,22 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>110.4</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7853,19 +7853,19 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:19</t>
+          <t>2026-07-01 06:06:15</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -7880,22 +7880,22 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>114.2</t>
+          <t>134.6</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7910,14 +7910,14 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>14.5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:20</t>
+          <t>2026-07-01 06:06:16</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -7969,7 +7969,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:21</t>
+          <t>2026-07-01 06:06:17</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -7984,12 +7984,12 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7999,17 +7999,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>1003.0</t>
+          <t>1002.8</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -8021,7 +8021,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:22</t>
+          <t>2026-07-01 06:06:18</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -8036,7 +8036,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8051,17 +8051,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -8073,7 +8073,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:23</t>
+          <t>2026-07-01 06:06:19</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -8125,7 +8125,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:24</t>
+          <t>2026-07-01 06:06:20</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -8140,22 +8140,22 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8165,19 +8165,19 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:25</t>
+          <t>2026-07-01 06:06:21</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -8192,22 +8192,22 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138.6</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>1003.9</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8229,7 +8229,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:26</t>
+          <t>2026-07-01 06:06:22</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -8244,22 +8244,22 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8269,19 +8269,19 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:27</t>
+          <t>2026-07-01 06:06:23</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -8296,7 +8296,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>118.8</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.3</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -8333,7 +8333,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:28</t>
+          <t>2026-07-01 06:06:24</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -8348,22 +8348,22 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>157.8</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8378,14 +8378,14 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:29</t>
+          <t>2026-07-01 06:06:25</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -8400,17 +8400,17 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>125.8</t>
+          <t>128.6</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8430,14 +8430,14 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:30</t>
+          <t>2026-07-01 06:06:27</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -8452,27 +8452,27 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>181.6</t>
+          <t>181.8</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -8489,7 +8489,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:31</t>
+          <t>2026-07-01 06:06:28</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -8541,7 +8541,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:32</t>
+          <t>2026-07-01 06:06:29</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -8593,7 +8593,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:33</t>
+          <t>2026-07-01 06:06:30</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -8608,12 +8608,12 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8623,17 +8623,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>1003.0</t>
+          <t>1002.8</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -8645,7 +8645,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:35</t>
+          <t>2026-07-01 06:06:31</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -8660,7 +8660,7 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>1003.8</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -8697,7 +8697,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:36</t>
+          <t>2026-07-01 06:06:33</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -8712,7 +8712,7 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>1003.9</t>
+          <t>1003.6</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -8749,7 +8749,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:37</t>
+          <t>2026-07-01 06:06:34</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -8764,7 +8764,7 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>1004.2</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:38</t>
+          <t>2026-07-01 06:06:35</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -8816,22 +8816,22 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>128.6</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -8841,19 +8841,19 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>1004.9</t>
+          <t>1004.8</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:39</t>
+          <t>2026-07-01 06:06:36</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -8905,7 +8905,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:40</t>
+          <t>2026-07-01 06:06:37</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -8920,17 +8920,17 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>125.8</t>
+          <t>128.6</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8950,14 +8950,14 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:41</t>
+          <t>2026-07-01 06:06:38</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -9009,7 +9009,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:42</t>
+          <t>2026-07-01 06:06:39</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -9024,7 +9024,7 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -9061,7 +9061,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:43</t>
+          <t>2026-07-01 06:06:40</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -9076,7 +9076,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -9086,34 +9086,34 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.3</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:44</t>
+          <t>2026-07-01 06:06:41</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -9128,44 +9128,44 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>102.8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:45</t>
+          <t>2026-07-01 06:06:42</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -9180,7 +9180,7 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -9195,17 +9195,17 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -9217,7 +9217,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:46</t>
+          <t>2026-07-01 06:06:43</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -9232,17 +9232,17 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>125.8</t>
+          <t>128.6</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9262,14 +9262,14 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:47</t>
+          <t>2026-07-01 06:06:44</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -9284,22 +9284,22 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>182.2</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9321,7 +9321,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:48</t>
+          <t>2026-07-01 06:06:45</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -9336,7 +9336,7 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -9366,14 +9366,14 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:49</t>
+          <t>2026-07-01 06:06:46</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -9388,44 +9388,44 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>160.8</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>1004.9</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:50</t>
+          <t>2026-07-01 06:06:47</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -9440,17 +9440,17 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>178.6</t>
+          <t>184.4</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -9465,19 +9465,19 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>1002.6</t>
+          <t>1002.2</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:51</t>
+          <t>2026-07-01 06:06:49</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -9492,32 +9492,32 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>173.6</t>
+          <t>176.4</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>1002.6</t>
+          <t>1002.4</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -9529,7 +9529,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:52</t>
+          <t>2026-07-01 06:06:50</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -9544,32 +9544,32 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>173.6</t>
+          <t>176.4</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>1002.6</t>
+          <t>1002.4</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -9581,7 +9581,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:53</t>
+          <t>2026-07-01 06:06:51</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -9596,7 +9596,7 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>1003.9</t>
+          <t>1003.6</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -9633,7 +9633,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:54</t>
+          <t>2026-07-01 06:06:52</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -9648,44 +9648,44 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>102.8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.7</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:55</t>
+          <t>2026-07-01 06:06:53</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -9700,7 +9700,7 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>1004.0</t>
+          <t>1003.8</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -9737,7 +9737,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:57</t>
+          <t>2026-07-01 06:06:54</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -9789,7 +9789,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:58</t>
+          <t>2026-07-01 06:06:55</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -9804,27 +9804,27 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -9834,14 +9834,14 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-01 05:46:59</t>
+          <t>2026-07-01 06:06:56</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -9856,7 +9856,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>1003.9</t>
+          <t>1003.6</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -9893,7 +9893,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:00</t>
+          <t>2026-07-01 06:06:57</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -9908,7 +9908,7 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.4</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9933,19 +9933,19 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.5</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:01</t>
+          <t>2026-07-01 06:06:58</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -9960,7 +9960,7 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -9975,29 +9975,29 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>1004.2</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:02</t>
+          <t>2026-07-01 06:06:59</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -10012,17 +10012,17 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>157.4</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>1003.7</t>
+          <t>1003.6</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -10049,7 +10049,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:03</t>
+          <t>2026-07-01 06:07:00</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -10064,7 +10064,7 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>1003.8</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -10101,7 +10101,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:04</t>
+          <t>2026-07-01 06:07:01</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -10116,44 +10116,44 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>1003.4</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:05</t>
+          <t>2026-07-01 06:07:02</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -10205,7 +10205,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:06</t>
+          <t>2026-07-01 06:07:03</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -10220,22 +10220,22 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>121.2</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10245,19 +10245,19 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>1003.2</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:07</t>
+          <t>2026-07-01 06:07:04</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -10272,7 +10272,7 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10297,19 +10297,19 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1004.6</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:08</t>
+          <t>2026-07-01 06:07:06</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -10324,22 +10324,22 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>108.8</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10349,19 +10349,19 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>1002.5</t>
+          <t>1002.4</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:09</t>
+          <t>2026-07-01 06:07:07</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -10413,7 +10413,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:10</t>
+          <t>2026-07-01 06:07:08</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -10465,7 +10465,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:11</t>
+          <t>2026-07-01 06:07:09</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -10480,7 +10480,7 @@
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -10505,19 +10505,19 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>1004.7</t>
+          <t>1004.9</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:12</t>
+          <t>2026-07-01 06:07:10</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -10532,22 +10532,22 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>998.7</t>
+          <t>998.9</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -10569,7 +10569,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:13</t>
+          <t>2026-07-01 06:07:11</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -10584,22 +10584,22 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>9.40</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>121.8</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>999.5</t>
+          <t>999.7</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -10621,7 +10621,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:14</t>
+          <t>2026-07-01 06:07:12</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -10636,22 +10636,22 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>998.7</t>
+          <t>998.9</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -10673,7 +10673,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:15</t>
+          <t>2026-07-01 06:07:13</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -10688,7 +10688,7 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>1004.4</t>
+          <t>1004.3</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -10725,7 +10725,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:16</t>
+          <t>2026-07-01 06:07:14</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -10740,7 +10740,7 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -10765,19 +10765,19 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>1003.4</t>
+          <t>1003.2</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:17</t>
+          <t>2026-07-01 06:07:15</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -10792,22 +10792,22 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>134.4</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -10817,19 +10817,19 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>1004.9</t>
+          <t>1004.8</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:18</t>
+          <t>2026-07-01 06:07:16</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -10844,7 +10844,7 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -10859,29 +10859,29 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:20</t>
+          <t>2026-07-01 06:07:17</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -10933,7 +10933,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:21</t>
+          <t>2026-07-01 06:07:18</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -10948,7 +10948,7 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>1004.5</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -10985,7 +10985,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:22</t>
+          <t>2026-07-01 06:07:19</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -11000,7 +11000,7 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -11010,34 +11010,34 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>148.4</t>
+          <t>151.2</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1005.0</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:23</t>
+          <t>2026-07-01 06:07:20</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -11052,7 +11052,7 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.2</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -11089,7 +11089,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:24</t>
+          <t>2026-07-01 06:07:21</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -11104,44 +11104,44 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>1002.9</t>
+          <t>1003.2</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>9.7</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:25</t>
+          <t>2026-07-01 06:07:23</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -11156,7 +11156,7 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -11181,19 +11181,19 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>1004.3</t>
+          <t>1004.2</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>12.9</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:26</t>
+          <t>2026-07-01 06:07:24</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -11208,7 +11208,7 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -11223,29 +11223,29 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>1004.2</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.7</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:27</t>
+          <t>2026-07-01 06:07:25</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -11260,22 +11260,22 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -11290,14 +11290,14 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:28</t>
+          <t>2026-07-01 06:07:26</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -11312,22 +11312,22 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>128.6</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -11337,19 +11337,19 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>1004.9</t>
+          <t>1004.8</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:29</t>
+          <t>2026-07-01 06:07:27</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -11364,7 +11364,7 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -11374,34 +11374,34 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.3</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:30</t>
+          <t>2026-07-01 06:07:28</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -11416,22 +11416,22 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>110.4</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -11441,19 +11441,19 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.4</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:31</t>
+          <t>2026-07-01 06:07:29</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -11468,22 +11468,22 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -11498,14 +11498,14 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:32</t>
+          <t>2026-07-01 06:07:30</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -11520,22 +11520,22 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>79.67</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:33</t>
+          <t>2026-07-01 06:07:31</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -11572,7 +11572,7 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -11582,34 +11582,34 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>148.4</t>
+          <t>151.2</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>1004.8</t>
+          <t>1005.0</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:34</t>
+          <t>2026-07-01 06:07:32</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -11624,7 +11624,7 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -11634,12 +11634,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -11661,7 +11661,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:35</t>
+          <t>2026-07-01 06:07:33</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -11676,7 +11676,7 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -11701,19 +11701,19 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>1002.2</t>
+          <t>1002.1</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:36</t>
+          <t>2026-07-01 06:07:34</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -11728,7 +11728,7 @@
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -11753,19 +11753,19 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>1003.4</t>
+          <t>1003.2</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:37</t>
+          <t>2026-07-01 06:07:35</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -11780,7 +11780,7 @@
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>1002.8</t>
+          <t>1002.7</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:38</t>
+          <t>2026-07-01 06:07:36</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -11869,7 +11869,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:39</t>
+          <t>2026-07-01 06:07:37</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -11884,7 +11884,7 @@
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -11899,17 +11899,17 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>1002.6</t>
+          <t>1002.8</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -11921,7 +11921,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:40</t>
+          <t>2026-07-01 06:07:38</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -11936,7 +11936,7 @@
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -11951,17 +11951,17 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>1002.6</t>
+          <t>1002.8</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -11973,7 +11973,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:41</t>
+          <t>2026-07-01 06:07:39</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -12025,7 +12025,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:43</t>
+          <t>2026-07-01 06:07:41</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -12040,7 +12040,7 @@
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>1004.2</t>
+          <t>1004.1</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -12077,7 +12077,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:44</t>
+          <t>2026-07-01 06:07:42</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -12129,7 +12129,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:45</t>
+          <t>2026-07-01 06:07:43</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -12144,12 +12144,12 @@
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-07-01 10:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -12169,19 +12169,19 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:46</t>
+          <t>2026-07-01 06:07:44</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -12196,32 +12196,32 @@
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>143.6</t>
+          <t>156.2</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>1003.1</t>
+          <t>1003.4</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -12233,7 +12233,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:47</t>
+          <t>2026-07-01 06:07:45</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -12248,17 +12248,17 @@
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>157.4</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -12273,19 +12273,19 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>1003.7</t>
+          <t>1003.6</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:48</t>
+          <t>2026-07-01 06:07:46</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -12337,7 +12337,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:49</t>
+          <t>2026-07-01 06:07:47</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -12352,17 +12352,17 @@
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>138.4</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -12377,19 +12377,19 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>1003.3</t>
+          <t>1003.2</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:50</t>
+          <t>2026-07-01 06:07:48</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -12404,7 +12404,7 @@
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -12414,17 +12414,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>113.6</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -12441,7 +12441,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:51</t>
+          <t>2026-07-01 06:07:49</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -12456,12 +12456,12 @@
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>1003.8</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -12493,7 +12493,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:52</t>
+          <t>2026-07-01 06:07:50</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -12508,7 +12508,7 @@
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -12523,17 +12523,17 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>1003.3</t>
+          <t>1003.2</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -12545,7 +12545,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:53</t>
+          <t>2026-07-01 06:07:51</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -12560,7 +12560,7 @@
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -12575,17 +12575,17 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>1003.3</t>
+          <t>1003.2</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -12597,7 +12597,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:54</t>
+          <t>2026-07-01 06:07:52</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -12612,7 +12612,7 @@
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:45:00.0</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -12627,17 +12627,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>1002.2</t>
+          <t>1002.0</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -12649,7 +12649,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:55</t>
+          <t>2026-07-01 06:07:53</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -12701,7 +12701,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:56</t>
+          <t>2026-07-01 06:07:54</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -12716,22 +12716,22 @@
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>80.69</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -12753,7 +12753,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:57</t>
+          <t>2026-07-01 06:07:55</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -12768,22 +12768,22 @@
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>109.2</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -12798,14 +12798,14 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:58</t>
+          <t>2026-07-01 06:07:56</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -12820,17 +12820,17 @@
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>121.2</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -12850,14 +12850,14 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-07-01 05:47:59</t>
+          <t>2026-07-01 06:07:57</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -12872,22 +12872,22 @@
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>19.80</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>118.8</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -12897,19 +12897,19 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>1004.2</t>
+          <t>1004.1</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:00</t>
+          <t>2026-07-01 06:07:59</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -12924,17 +12924,17 @@
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-07-01 11:00:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>121.2</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -12954,14 +12954,14 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:01</t>
+          <t>2026-07-01 06:08:00</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -13013,7 +13013,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:02</t>
+          <t>2026-07-01 06:08:01</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -13028,22 +13028,22 @@
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -13053,19 +13053,19 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>1005.6</t>
+          <t>1005.9</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:03</t>
+          <t>2026-07-01 06:08:02</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -13080,22 +13080,22 @@
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -13105,19 +13105,19 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>1005.6</t>
+          <t>1005.9</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:04</t>
+          <t>2026-07-01 06:08:03</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -13132,12 +13132,12 @@
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-07-01 10:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -13157,19 +13157,19 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1004.0</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:05</t>
+          <t>2026-07-01 06:08:04</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -13184,22 +13184,22 @@
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>1003.9</t>
+          <t>1003.8</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -13221,7 +13221,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:06</t>
+          <t>2026-07-01 06:08:05</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -13236,7 +13236,7 @@
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -13261,19 +13261,19 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>1003.6</t>
+          <t>1003.5</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:07</t>
+          <t>2026-07-01 06:08:06</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -13288,7 +13288,7 @@
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>118.8</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>1004.5</t>
+          <t>1004.3</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -13325,7 +13325,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:08</t>
+          <t>2026-07-01 06:08:07</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -13340,7 +13340,7 @@
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>1004.5</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -13377,7 +13377,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:10</t>
+          <t>2026-07-01 06:08:08</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -13392,7 +13392,7 @@
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -13402,12 +13402,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -13429,7 +13429,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:11</t>
+          <t>2026-07-01 06:08:09</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -13444,7 +13444,7 @@
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-07-01 11:15:00.0</t>
+          <t>2026-07-01 11:30:00.0</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -13454,22 +13454,22 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>1003.9</t>
+          <t>1003.7</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -13481,7 +13481,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:12</t>
+          <t>2026-07-01 06:08:10</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -13533,7 +13533,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:13</t>
+          <t>2026-07-01 06:08:11</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -13585,7 +13585,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:14</t>
+          <t>2026-07-01 06:08:12</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -13637,7 +13637,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-07-01 05:48:15</t>
+          <t>2026-07-01 06:08:14</t>
         </is>
       </c>
       <c r="B255" t="n">
